--- a/supplementary_material/metrics_summary.xlsx
+++ b/supplementary_material/metrics_summary.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\futbo\Desktop\eukaryo_methods\supplementary_material\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4029E9A8-31A6-4E13-AB06-CA04B464F434}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E11F16E1-FD72-4C73-8EA4-41620360F468}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="214" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="217" uniqueCount="86">
   <si>
     <t>reactions</t>
   </si>
@@ -278,6 +278,9 @@
   </si>
   <si>
     <t>Number of genes</t>
+  </si>
+  <si>
+    <t>PlantSEED</t>
   </si>
 </sst>
 </file>
@@ -976,7 +979,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AL10"/>
+  <dimension ref="A1:AL11"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="16.6328125" customWidth="1"/>
@@ -1481,338 +1484,338 @@
     </row>
     <row r="5" spans="1:38" x14ac:dyDescent="0.35">
       <c r="A5" s="1" t="s">
-        <v>40</v>
+        <v>85</v>
       </c>
       <c r="B5">
-        <v>2626</v>
+        <v>1121</v>
       </c>
       <c r="C5">
-        <v>5509</v>
+        <v>1</v>
       </c>
       <c r="D5">
-        <v>2043</v>
+        <v>1101</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>115</v>
       </c>
       <c r="F5">
-        <v>1316</v>
+        <v>726</v>
       </c>
       <c r="G5">
-        <v>2442</v>
+        <v>529</v>
       </c>
       <c r="H5">
-        <v>0</v>
+        <v>98</v>
       </c>
       <c r="I5" s="2">
-        <v>2.0978674790555978</v>
+        <v>8.9206066012488853E-4</v>
       </c>
       <c r="J5">
-        <v>2580</v>
+        <v>1179</v>
       </c>
       <c r="K5">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="L5">
-        <v>2564</v>
+        <v>1101</v>
       </c>
       <c r="M5" s="2">
-        <v>0.73487986628917745</v>
+        <v>0.54291371480472306</v>
       </c>
       <c r="N5" s="2">
-        <v>0.34310736104095219</v>
+        <v>0.30050928554050771</v>
       </c>
       <c r="O5" s="2">
-        <v>0.49002205050903658</v>
+        <v>0.39141094651458852</v>
       </c>
       <c r="P5">
-        <v>4</v>
+        <v>0.2</v>
       </c>
       <c r="Q5" s="2">
-        <v>8.0549682875264275E-2</v>
+        <v>6.4242852100247091E-2</v>
       </c>
       <c r="R5" s="2">
-        <v>8.5101630556176006E-2</v>
+        <v>6.019830028328612E-2</v>
       </c>
       <c r="S5" s="2">
-        <v>0.20205066344993969</v>
+        <v>0</v>
       </c>
       <c r="T5" s="2">
-        <v>0.22222222222222221</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="U5">
-        <v>2728</v>
+        <v>632</v>
       </c>
       <c r="V5">
-        <v>2374</v>
+        <v>510</v>
       </c>
       <c r="W5" s="2">
-        <v>0.6382538842828489</v>
+        <v>0</v>
       </c>
       <c r="X5" s="2">
-        <v>0.41451887250534802</v>
+        <v>0</v>
       </c>
       <c r="Y5" s="2">
-        <v>0.45945945945945948</v>
+        <v>0.56756756756756754</v>
       </c>
       <c r="Z5">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="AA5">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AB5">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="AC5" s="2">
-        <v>0.46248679112363511</v>
+        <v>0.19742867206762951</v>
       </c>
       <c r="AD5" s="2">
-        <v>0.5395232120451694</v>
+        <v>0.24654956085319951</v>
       </c>
       <c r="AE5" s="2">
-        <v>0.87353372434017595</v>
+        <v>0.26521191775073438</v>
       </c>
       <c r="AF5" s="2">
-        <v>0.95571658615136879</v>
+        <v>0.20531400966183569</v>
       </c>
       <c r="AG5" s="2">
-        <v>0.18170266836086399</v>
+        <v>9.99000999000999E-4</v>
       </c>
       <c r="AH5" s="2">
-        <v>0.77798933739527798</v>
+        <v>0.98215878679750224</v>
       </c>
       <c r="AI5" s="2">
-        <v>0.50114242193450109</v>
+        <v>0.64763603925066904</v>
       </c>
       <c r="AJ5" s="2">
-        <v>0.33333333333333331</v>
+        <v>0.81818181818181823</v>
       </c>
       <c r="AK5" s="2">
-        <v>0.94444444444444442</v>
+        <v>0.58333333333333337</v>
       </c>
       <c r="AL5" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:38" x14ac:dyDescent="0.35">
       <c r="A6" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B6">
-        <v>2573</v>
+        <v>2626</v>
       </c>
       <c r="C6">
-        <v>4604</v>
+        <v>5509</v>
       </c>
       <c r="D6">
-        <v>2431</v>
+        <v>2043</v>
       </c>
       <c r="E6">
-        <v>683</v>
+        <v>0</v>
       </c>
       <c r="F6">
-        <v>0</v>
+        <v>1316</v>
       </c>
       <c r="G6">
-        <v>3053</v>
+        <v>2442</v>
       </c>
       <c r="H6">
-        <v>591</v>
+        <v>0</v>
       </c>
       <c r="I6" s="2">
-        <v>1.7893509521958799</v>
+        <v>2.0978674790555978</v>
       </c>
       <c r="J6">
-        <v>3053</v>
+        <v>2580</v>
       </c>
       <c r="K6">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L6">
-        <v>2561</v>
+        <v>2564</v>
       </c>
       <c r="M6" s="2">
-        <v>0.39086294416243661</v>
+        <v>0.73487986628917745</v>
       </c>
       <c r="N6" s="2">
-        <v>0.20818692369744951</v>
+        <v>0.34310736104095219</v>
       </c>
       <c r="O6" s="2">
-        <v>0.2766904313718197</v>
+        <v>0.49002205050903658</v>
       </c>
       <c r="P6">
-        <v>1.2</v>
+        <v>4</v>
       </c>
       <c r="Q6" s="2">
-        <v>9.0100111234705224E-2</v>
+        <v>8.0549682875264275E-2</v>
       </c>
       <c r="R6" s="2">
-        <v>9.6473449533846775E-2</v>
+        <v>8.5101630556176006E-2</v>
       </c>
       <c r="S6" s="2">
-        <v>0.2986111111111111</v>
+        <v>0.20205066344993969</v>
       </c>
       <c r="T6" s="2">
-        <v>0</v>
+        <v>0.22222222222222221</v>
       </c>
       <c r="U6">
-        <v>2517</v>
+        <v>2728</v>
       </c>
       <c r="V6">
-        <v>2926</v>
+        <v>2374</v>
       </c>
       <c r="W6" s="2">
-        <v>0.62084635204146277</v>
+        <v>0.6382538842828489</v>
       </c>
       <c r="X6" s="2">
-        <v>0.29758879360567131</v>
+        <v>0.41451887250534802</v>
       </c>
       <c r="Y6" s="2">
-        <v>0.60810810810810811</v>
+        <v>0.45945945945945948</v>
       </c>
       <c r="Z6">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="AA6">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="AB6">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="AC6" s="2">
-        <v>0.45315251849242688</v>
+        <v>0.46248679112363511</v>
       </c>
       <c r="AD6" s="2">
-        <v>0.63843580092011709</v>
+        <v>0.5395232120451694</v>
       </c>
       <c r="AE6" s="2">
-        <v>0.94676201827572504</v>
+        <v>0.87353372434017595</v>
       </c>
       <c r="AF6" s="2">
-        <v>0.84894053315105944</v>
+        <v>0.95571658615136879</v>
       </c>
       <c r="AG6" s="2">
-        <v>0.21741963509991311</v>
+        <v>0.18170266836086399</v>
       </c>
       <c r="AH6" s="2">
-        <v>0.94481150408083947</v>
+        <v>0.77798933739527798</v>
       </c>
       <c r="AI6" s="2">
-        <v>0</v>
+        <v>0.50114242193450109</v>
       </c>
       <c r="AJ6" s="2">
-        <v>0.1111111111111111</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="AK6" s="2">
-        <v>0.80555555555555558</v>
+        <v>0.94444444444444442</v>
       </c>
       <c r="AL6" s="2">
-        <v>0.55172413793103448</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:38" x14ac:dyDescent="0.35">
       <c r="A7" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B7">
-        <v>1723</v>
+        <v>2573</v>
       </c>
       <c r="C7">
-        <v>3452</v>
+        <v>4604</v>
       </c>
       <c r="D7">
-        <v>1581</v>
+        <v>2431</v>
       </c>
       <c r="E7">
-        <v>147</v>
+        <v>683</v>
       </c>
       <c r="F7">
         <v>0</v>
       </c>
       <c r="G7">
-        <v>1897</v>
+        <v>3053</v>
       </c>
       <c r="H7">
-        <v>105</v>
+        <v>591</v>
       </c>
       <c r="I7" s="2">
-        <v>2.003482298316889</v>
+        <v>1.7893509521958799</v>
       </c>
       <c r="J7">
-        <v>1897</v>
+        <v>3053</v>
       </c>
       <c r="K7">
         <v>1</v>
       </c>
       <c r="L7">
-        <v>1723</v>
+        <v>2561</v>
       </c>
       <c r="M7" s="2">
-        <v>0.53081834010446893</v>
+        <v>0.39086294416243661</v>
       </c>
       <c r="N7" s="2">
-        <v>0.17489212384661029</v>
+        <v>0.20818692369744951</v>
       </c>
       <c r="O7" s="2">
-        <v>0.30836445494330722</v>
+        <v>0.2766904313718197</v>
       </c>
       <c r="P7">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="Q7" s="2">
-        <v>0.1030204962243797</v>
+        <v>9.0100111234705224E-2</v>
       </c>
       <c r="R7" s="2">
-        <v>0.1118186449312277</v>
+        <v>9.6473449533846775E-2</v>
       </c>
       <c r="S7" s="2">
-        <v>0.34404821697639382</v>
+        <v>0.2986111111111111</v>
       </c>
       <c r="T7" s="2">
         <v>0</v>
       </c>
       <c r="U7">
-        <v>1707</v>
+        <v>2517</v>
       </c>
       <c r="V7">
-        <v>1881</v>
+        <v>2926</v>
       </c>
       <c r="W7" s="2">
-        <v>0.63345363199538918</v>
+        <v>0.62084635204146277</v>
       </c>
       <c r="X7" s="2">
-        <v>0.32390288103326248</v>
+        <v>0.29758879360567131</v>
       </c>
       <c r="Y7" s="2">
-        <v>0.39189189189189189</v>
+        <v>0.60810810810810811</v>
       </c>
       <c r="Z7">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AA7">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="AB7">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="AC7" s="2">
-        <v>0.30345191969003171</v>
+        <v>0.45315251849242688</v>
       </c>
       <c r="AD7" s="2">
-        <v>0.39669594312003348</v>
+        <v>0.63843580092011709</v>
       </c>
       <c r="AE7" s="2">
-        <v>0.71632396139320187</v>
+        <v>0.94676201827572504</v>
       </c>
       <c r="AF7" s="2">
-        <v>0.75724637681159424</v>
+        <v>0.84894053315105944</v>
       </c>
       <c r="AG7" s="2">
-        <v>0.28997682502896871</v>
+        <v>0.21741963509991311</v>
       </c>
       <c r="AH7" s="2">
-        <v>0.9175856065002902</v>
+        <v>0.94481150408083947</v>
       </c>
       <c r="AI7" s="2">
         <v>0</v>
@@ -1821,357 +1824,473 @@
         <v>0.1111111111111111</v>
       </c>
       <c r="AK7" s="2">
-        <v>0.77777777777777779</v>
+        <v>0.80555555555555558</v>
       </c>
       <c r="AL7" s="2">
-        <v>3.5714285714285712E-2</v>
+        <v>0.55172413793103448</v>
       </c>
     </row>
     <row r="8" spans="1:38" x14ac:dyDescent="0.35">
       <c r="A8" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B8">
-        <v>1365</v>
+        <v>1723</v>
       </c>
       <c r="C8">
-        <v>3677</v>
+        <v>3452</v>
       </c>
       <c r="D8">
-        <v>1365</v>
+        <v>1581</v>
       </c>
       <c r="E8">
-        <v>545</v>
+        <v>147</v>
       </c>
       <c r="F8">
-        <v>256</v>
+        <v>0</v>
       </c>
       <c r="G8">
-        <v>1753</v>
+        <v>1897</v>
       </c>
       <c r="H8">
-        <v>479</v>
+        <v>105</v>
       </c>
       <c r="I8" s="2">
-        <v>2.693772893772894</v>
+        <v>2.003482298316889</v>
       </c>
       <c r="J8">
-        <v>1753</v>
+        <v>1897</v>
       </c>
       <c r="K8">
         <v>1</v>
       </c>
       <c r="L8">
-        <v>1353</v>
+        <v>1723</v>
       </c>
       <c r="M8" s="2">
-        <v>0.45664063755262052</v>
+        <v>0.53081834010446893</v>
       </c>
       <c r="N8" s="2">
-        <v>0.1978863857453976</v>
+        <v>0.17489212384661029</v>
       </c>
       <c r="O8" s="2">
-        <v>0.29491923017310617</v>
+        <v>0.30836445494330722</v>
       </c>
       <c r="P8">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="Q8" s="2">
-        <v>6.7567567567567571E-2</v>
+        <v>0.1030204962243797</v>
       </c>
       <c r="R8" s="2">
-        <v>8.3762886597938138E-2</v>
+        <v>0.1118186449312277</v>
       </c>
       <c r="S8" s="2">
-        <v>0.28869323447636702</v>
+        <v>0.34404821697639382</v>
       </c>
       <c r="T8" s="2">
         <v>0</v>
       </c>
       <c r="U8">
-        <v>1330</v>
+        <v>1707</v>
       </c>
       <c r="V8">
-        <v>1721</v>
+        <v>1881</v>
       </c>
       <c r="W8" s="2">
-        <v>0.64585200414354027</v>
+        <v>0.63345363199538918</v>
       </c>
       <c r="X8" s="2">
-        <v>0</v>
+        <v>0.32390288103326248</v>
       </c>
       <c r="Y8" s="2">
-        <v>0.64864864864864868</v>
+        <v>0.39189189189189189</v>
       </c>
       <c r="Z8">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="AA8">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="AB8">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="AC8" s="2">
-        <v>0.24040154984149351</v>
+        <v>0.30345191969003171</v>
       </c>
       <c r="AD8" s="2">
-        <v>0.36658301965704732</v>
+        <v>0.39669594312003348</v>
       </c>
       <c r="AE8" s="2">
-        <v>0.55812001678556444</v>
+        <v>0.71632396139320187</v>
       </c>
       <c r="AF8" s="2">
-        <v>0.69283413848631237</v>
+        <v>0.75724637681159424</v>
       </c>
       <c r="AG8" s="2">
-        <v>0.27223279847701931</v>
+        <v>0.28997682502896871</v>
       </c>
       <c r="AH8" s="2">
-        <v>1</v>
+        <v>0.9175856065002902</v>
       </c>
       <c r="AI8" s="2">
-        <v>0.18754578754578749</v>
+        <v>0</v>
       </c>
       <c r="AJ8" s="2">
         <v>0.1111111111111111</v>
       </c>
       <c r="AK8" s="2">
-        <v>0.94444444444444442</v>
+        <v>0.77777777777777779</v>
       </c>
       <c r="AL8" s="2">
-        <v>0.41176470588235292</v>
+        <v>3.5714285714285712E-2</v>
       </c>
     </row>
     <row r="9" spans="1:38" x14ac:dyDescent="0.35">
       <c r="A9" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B9">
-        <v>1381</v>
+        <v>1365</v>
       </c>
       <c r="C9">
-        <v>1392</v>
+        <v>3677</v>
       </c>
       <c r="D9">
-        <v>1244</v>
+        <v>1365</v>
       </c>
       <c r="E9">
-        <v>108</v>
+        <v>545</v>
       </c>
       <c r="F9">
-        <v>702</v>
+        <v>256</v>
       </c>
       <c r="G9">
-        <v>1426</v>
+        <v>1753</v>
       </c>
       <c r="H9">
-        <v>108</v>
+        <v>479</v>
       </c>
       <c r="I9" s="2">
-        <v>1.007965242577842</v>
+        <v>2.693772893772894</v>
       </c>
       <c r="J9">
-        <v>1463</v>
+        <v>1753</v>
       </c>
       <c r="K9">
+        <v>1</v>
+      </c>
+      <c r="L9">
+        <v>1353</v>
+      </c>
+      <c r="M9" s="2">
+        <v>0.45664063755262052</v>
+      </c>
+      <c r="N9" s="2">
+        <v>0.1978863857453976</v>
+      </c>
+      <c r="O9" s="2">
+        <v>0.29491923017310617</v>
+      </c>
+      <c r="P9">
+        <v>0.2</v>
+      </c>
+      <c r="Q9" s="2">
+        <v>6.7567567567567571E-2</v>
+      </c>
+      <c r="R9" s="2">
+        <v>8.3762886597938138E-2</v>
+      </c>
+      <c r="S9" s="2">
+        <v>0.28869323447636702</v>
+      </c>
+      <c r="T9" s="2">
+        <v>0</v>
+      </c>
+      <c r="U9">
+        <v>1330</v>
+      </c>
+      <c r="V9">
+        <v>1721</v>
+      </c>
+      <c r="W9" s="2">
+        <v>0.64585200414354027</v>
+      </c>
+      <c r="X9" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y9" s="2">
+        <v>0.64864864864864868</v>
+      </c>
+      <c r="Z9">
         <v>2</v>
       </c>
-      <c r="L9">
-        <v>1293</v>
-      </c>
-      <c r="M9" s="2">
-        <v>0.67977555613393148</v>
-      </c>
-      <c r="N9" s="2">
-        <v>9.3218158291522371E-2</v>
-      </c>
-      <c r="O9" s="2">
-        <v>0.31317718248242582</v>
-      </c>
-      <c r="P9">
-        <v>2</v>
-      </c>
-      <c r="Q9" s="2">
-        <v>0.1101617332926457</v>
-      </c>
-      <c r="R9" s="2">
-        <v>0.1013837898898616</v>
-      </c>
-      <c r="S9" s="2">
-        <v>0</v>
-      </c>
-      <c r="T9" s="2">
-        <v>0.22222222222222221</v>
-      </c>
-      <c r="U9">
-        <v>1255</v>
-      </c>
-      <c r="V9">
-        <v>1416</v>
-      </c>
-      <c r="W9" s="2">
-        <v>0</v>
-      </c>
-      <c r="X9" s="2">
-        <v>0.13148959837388549</v>
-      </c>
-      <c r="Y9" s="2">
-        <v>0.68918918918918914</v>
-      </c>
-      <c r="Z9">
-        <v>10</v>
-      </c>
       <c r="AA9">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="AB9">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="AC9" s="2">
-        <v>0.24321944346600921</v>
+        <v>0.24040154984149351</v>
       </c>
       <c r="AD9" s="2">
-        <v>0.30593893768297781</v>
+        <v>0.36658301965704732</v>
       </c>
       <c r="AE9" s="2">
-        <v>0.52664708350818301</v>
+        <v>0.55812001678556444</v>
       </c>
       <c r="AF9" s="2">
-        <v>0.57004830917874394</v>
+        <v>0.69283413848631237</v>
       </c>
       <c r="AG9" s="2">
-        <v>0.7191091954022989</v>
+        <v>0.27223279847701931</v>
       </c>
       <c r="AH9" s="2">
-        <v>0.90079652425778423</v>
+        <v>1</v>
       </c>
       <c r="AI9" s="2">
-        <v>0.50832729905865315</v>
+        <v>0.18754578754578749</v>
       </c>
       <c r="AJ9" s="2">
-        <v>0.22222222222222221</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="AK9" s="2">
-        <v>0.72222222222222221</v>
+        <v>0.94444444444444442</v>
       </c>
       <c r="AL9" s="2">
-        <v>0.96153846153846156</v>
+        <v>0.41176470588235292</v>
       </c>
     </row>
     <row r="10" spans="1:38" x14ac:dyDescent="0.35">
       <c r="A10" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B10">
+        <v>1381</v>
+      </c>
+      <c r="C10">
+        <v>1392</v>
+      </c>
+      <c r="D10">
+        <v>1244</v>
+      </c>
+      <c r="E10">
+        <v>108</v>
+      </c>
+      <c r="F10">
+        <v>702</v>
+      </c>
+      <c r="G10">
+        <v>1426</v>
+      </c>
+      <c r="H10">
+        <v>108</v>
+      </c>
+      <c r="I10" s="2">
+        <v>1.007965242577842</v>
+      </c>
+      <c r="J10">
+        <v>1463</v>
+      </c>
+      <c r="K10">
+        <v>2</v>
+      </c>
+      <c r="L10">
+        <v>1293</v>
+      </c>
+      <c r="M10" s="2">
+        <v>0.67977555613393148</v>
+      </c>
+      <c r="N10" s="2">
+        <v>9.3218158291522371E-2</v>
+      </c>
+      <c r="O10" s="2">
+        <v>0.31317718248242582</v>
+      </c>
+      <c r="P10">
+        <v>2</v>
+      </c>
+      <c r="Q10" s="2">
+        <v>0.1101617332926457</v>
+      </c>
+      <c r="R10" s="2">
+        <v>0.1013837898898616</v>
+      </c>
+      <c r="S10" s="2">
+        <v>0</v>
+      </c>
+      <c r="T10" s="2">
+        <v>0.22222222222222221</v>
+      </c>
+      <c r="U10">
+        <v>1255</v>
+      </c>
+      <c r="V10">
+        <v>1416</v>
+      </c>
+      <c r="W10" s="2">
+        <v>0</v>
+      </c>
+      <c r="X10" s="2">
+        <v>0.13148959837388549</v>
+      </c>
+      <c r="Y10" s="2">
+        <v>0.68918918918918914</v>
+      </c>
+      <c r="Z10">
+        <v>10</v>
+      </c>
+      <c r="AA10">
+        <v>25</v>
+      </c>
+      <c r="AB10">
+        <v>1</v>
+      </c>
+      <c r="AC10" s="2">
+        <v>0.24321944346600921</v>
+      </c>
+      <c r="AD10" s="2">
+        <v>0.30593893768297781</v>
+      </c>
+      <c r="AE10" s="2">
+        <v>0.52664708350818301</v>
+      </c>
+      <c r="AF10" s="2">
+        <v>0.57004830917874394</v>
+      </c>
+      <c r="AG10" s="2">
+        <v>0.7191091954022989</v>
+      </c>
+      <c r="AH10" s="2">
+        <v>0.90079652425778423</v>
+      </c>
+      <c r="AI10" s="2">
+        <v>0.50832729905865315</v>
+      </c>
+      <c r="AJ10" s="2">
+        <v>0.22222222222222221</v>
+      </c>
+      <c r="AK10" s="2">
+        <v>0.72222222222222221</v>
+      </c>
+      <c r="AL10" s="2">
+        <v>0.96153846153846156</v>
+      </c>
+    </row>
+    <row r="11" spans="1:38" x14ac:dyDescent="0.35">
+      <c r="A11" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="B10">
+      <c r="B11">
         <v>5678</v>
       </c>
-      <c r="C10">
+      <c r="C11">
         <v>1001</v>
       </c>
-      <c r="D10">
+      <c r="D11">
         <v>3502</v>
       </c>
-      <c r="E10">
+      <c r="E11">
         <v>391</v>
       </c>
-      <c r="F10">
-        <v>0</v>
-      </c>
-      <c r="G10">
+      <c r="F11">
+        <v>0</v>
+      </c>
+      <c r="G11">
         <v>2526</v>
       </c>
-      <c r="H10">
+      <c r="H11">
         <v>356</v>
       </c>
-      <c r="I10" s="2">
+      <c r="I11" s="2">
         <v>0.25818950334624868</v>
       </c>
-      <c r="J10">
+      <c r="J11">
         <v>4782</v>
       </c>
-      <c r="K10">
+      <c r="K11">
         <v>9</v>
       </c>
-      <c r="L10">
+      <c r="L11">
         <v>2975</v>
       </c>
-      <c r="M10" s="2">
+      <c r="M11" s="2">
         <v>0.5993486668023611</v>
       </c>
-      <c r="N10" s="2">
+      <c r="N11" s="2">
         <v>0.27725834692454332</v>
       </c>
-      <c r="O10" s="2">
+      <c r="O11" s="2">
         <v>0.39804221687872487</v>
       </c>
-      <c r="P10">
-        <v>0</v>
-      </c>
-      <c r="Q10" s="2">
-        <v>1</v>
-      </c>
-      <c r="R10" s="2">
-        <v>1</v>
-      </c>
-      <c r="S10" s="2">
-        <v>1</v>
-      </c>
-      <c r="T10" s="2">
-        <v>1</v>
-      </c>
-      <c r="U10">
+      <c r="P11">
+        <v>0</v>
+      </c>
+      <c r="Q11" s="2">
+        <v>1</v>
+      </c>
+      <c r="R11" s="2">
+        <v>1</v>
+      </c>
+      <c r="S11" s="2">
+        <v>1</v>
+      </c>
+      <c r="T11" s="2">
+        <v>1</v>
+      </c>
+      <c r="U11">
         <v>2383</v>
       </c>
-      <c r="V10">
+      <c r="V11">
         <v>2484</v>
       </c>
-      <c r="W10" s="2">
-        <v>1</v>
-      </c>
-      <c r="X10" s="2">
-        <v>1</v>
-      </c>
-      <c r="Y10" s="2">
+      <c r="W11" s="2">
+        <v>1</v>
+      </c>
+      <c r="X11" s="2">
+        <v>1</v>
+      </c>
+      <c r="Y11" s="2">
         <v>0.45945945945945948</v>
       </c>
-      <c r="Z10">
+      <c r="Z11">
         <v>19</v>
       </c>
-      <c r="AA10">
+      <c r="AA11">
         <v>17</v>
       </c>
-      <c r="AB10">
-        <v>0</v>
-      </c>
-      <c r="AC10" s="2">
-        <v>1</v>
-      </c>
-      <c r="AD10" s="2">
-        <v>1</v>
-      </c>
-      <c r="AE10" s="2">
-        <v>1</v>
-      </c>
-      <c r="AF10" s="2">
-        <v>1</v>
-      </c>
-      <c r="AG10" s="2">
-        <v>1</v>
-      </c>
-      <c r="AH10" s="2">
+      <c r="AB11">
+        <v>0</v>
+      </c>
+      <c r="AC11" s="2">
+        <v>1</v>
+      </c>
+      <c r="AD11" s="2">
+        <v>1</v>
+      </c>
+      <c r="AE11" s="2">
+        <v>1</v>
+      </c>
+      <c r="AF11" s="2">
+        <v>1</v>
+      </c>
+      <c r="AG11" s="2">
+        <v>1</v>
+      </c>
+      <c r="AH11" s="2">
         <v>0.61676646706586824</v>
       </c>
-      <c r="AI10" s="2">
-        <v>0</v>
-      </c>
-      <c r="AJ10" s="2">
-        <v>1</v>
-      </c>
-      <c r="AK10" s="2">
+      <c r="AI11" s="2">
+        <v>0</v>
+      </c>
+      <c r="AJ11" s="2">
+        <v>1</v>
+      </c>
+      <c r="AK11" s="2">
         <v>0.47222222222222221</v>
       </c>
-      <c r="AL10" s="2">
+      <c r="AL11" s="2">
         <v>1</v>
       </c>
     </row>
@@ -2182,7 +2301,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:AL10"/>
+  <dimension ref="A1:AL11"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="16.36328125" customWidth="1"/>
@@ -2683,338 +2802,338 @@
     </row>
     <row r="5" spans="1:38" x14ac:dyDescent="0.35">
       <c r="A5" s="1" t="s">
-        <v>40</v>
+        <v>85</v>
       </c>
       <c r="B5">
-        <v>3295</v>
+        <v>1121</v>
       </c>
       <c r="C5">
-        <v>3891</v>
+        <v>634</v>
       </c>
       <c r="D5">
-        <v>2652</v>
+        <v>1101</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>115</v>
       </c>
       <c r="F5">
-        <v>1803</v>
+        <v>726</v>
       </c>
       <c r="G5">
-        <v>2916</v>
+        <v>529</v>
       </c>
       <c r="H5">
-        <v>0</v>
+        <v>98</v>
       </c>
       <c r="I5" s="2">
-        <v>1.1808801213960549</v>
+        <v>0.5655664585191793</v>
       </c>
       <c r="J5">
-        <v>3112</v>
+        <v>1179</v>
       </c>
       <c r="K5">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="L5">
-        <v>3209</v>
+        <v>1101</v>
       </c>
       <c r="M5" s="2">
-        <v>0.53382655951091462</v>
+        <v>0.54291371480472306</v>
       </c>
       <c r="N5" s="2">
-        <v>0.35840515144478191</v>
+        <v>0.30050928554050771</v>
       </c>
       <c r="O5" s="2">
-        <v>0.42418817946958159</v>
-      </c>
-      <c r="P5" s="2">
-        <v>4</v>
+        <v>0.39141094651458852</v>
+      </c>
+      <c r="P5">
+        <v>0.2</v>
       </c>
       <c r="Q5" s="2">
-        <v>7.7325364213672018E-2</v>
+        <v>6.5399484536082478E-2</v>
       </c>
       <c r="R5" s="2">
-        <v>9.7014925373134331E-2</v>
+        <v>6.1840120663650078E-2</v>
       </c>
       <c r="S5" s="2">
-        <v>0.2464396284829721</v>
+        <v>9.0619307832422585E-2</v>
       </c>
       <c r="T5" s="2">
-        <v>0.22222222222222221</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="U5">
-        <v>3093</v>
+        <v>632</v>
       </c>
       <c r="V5">
-        <v>2839</v>
+        <v>510</v>
       </c>
       <c r="W5" s="2">
-        <v>0.57893406007577963</v>
+        <v>0.25433676796616927</v>
       </c>
       <c r="X5" s="2">
-        <v>0.36256669342252551</v>
+        <v>0</v>
       </c>
       <c r="Y5" s="2">
-        <v>0.48780487804878048</v>
+        <v>0.51219512195121952</v>
       </c>
       <c r="Z5">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="AA5">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AB5">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="AC5" s="2">
-        <v>0.49452198709290113</v>
+        <v>0.16824253339336631</v>
       </c>
       <c r="AD5" s="2">
-        <v>0.69838420107719923</v>
+        <v>0.26458707360861761</v>
       </c>
       <c r="AE5" s="2">
-        <v>0.86485612673779499</v>
+        <v>0.23626168224299071</v>
       </c>
       <c r="AF5" s="2">
-        <v>0.81225783726664313</v>
+        <v>0.2211621856027754</v>
       </c>
       <c r="AG5" s="2">
-        <v>0.45386790028270368</v>
+        <v>0.35900339750849369</v>
       </c>
       <c r="AH5" s="2">
-        <v>0.80485584218512896</v>
+        <v>0.98215878679750224</v>
       </c>
       <c r="AI5" s="2">
-        <v>0.54719271623672228</v>
+        <v>0.64763603925066904</v>
       </c>
       <c r="AJ5" s="2">
-        <v>0.33333333333333331</v>
+        <v>0.81818181818181823</v>
       </c>
       <c r="AK5" s="2">
-        <v>0.97560975609756095</v>
+        <v>0.51219512195121952</v>
       </c>
       <c r="AL5" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:38" x14ac:dyDescent="0.35">
       <c r="A6" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B6">
-        <v>3349</v>
+        <v>3295</v>
       </c>
       <c r="C6">
-        <v>2809</v>
+        <v>3891</v>
       </c>
       <c r="D6">
-        <v>3035</v>
+        <v>2652</v>
       </c>
       <c r="E6">
-        <v>872</v>
+        <v>0</v>
       </c>
       <c r="F6">
-        <v>0</v>
+        <v>1803</v>
       </c>
       <c r="G6">
-        <v>3717</v>
+        <v>2916</v>
       </c>
       <c r="H6">
-        <v>634</v>
+        <v>0</v>
       </c>
       <c r="I6" s="2">
-        <v>0.83875783816064498</v>
+        <v>1.1808801213960549</v>
       </c>
       <c r="J6">
-        <v>3717</v>
+        <v>3112</v>
       </c>
       <c r="K6">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L6">
-        <v>3333</v>
+        <v>3209</v>
       </c>
       <c r="M6" s="2">
-        <v>0.38655865586558658</v>
+        <v>0.53382655951091462</v>
       </c>
       <c r="N6" s="2">
-        <v>0.20751680437521461</v>
+        <v>0.35840515144478191</v>
       </c>
       <c r="O6" s="2">
-        <v>0.27465749868410411</v>
+        <v>0.42418817946958159</v>
       </c>
       <c r="P6" s="2">
-        <v>1.2</v>
+        <v>4</v>
       </c>
       <c r="Q6" s="2">
-        <v>0.10231696014828549</v>
+        <v>7.7325364213672018E-2</v>
       </c>
       <c r="R6" s="2">
-        <v>0.11018078020932449</v>
+        <v>9.7014925373134331E-2</v>
       </c>
       <c r="S6" s="2">
-        <v>0.34629294755877033</v>
+        <v>0.2464396284829721</v>
       </c>
       <c r="T6" s="2">
-        <v>0</v>
+        <v>0.22222222222222221</v>
       </c>
       <c r="U6">
-        <v>3272</v>
+        <v>3093</v>
       </c>
       <c r="V6">
-        <v>3528</v>
+        <v>2839</v>
       </c>
       <c r="W6" s="2">
-        <v>0.55572812751818845</v>
+        <v>0.57893406007577963</v>
       </c>
       <c r="X6" s="2">
-        <v>1.7182906095825321E-2</v>
+        <v>0.36256669342252551</v>
       </c>
       <c r="Y6" s="2">
-        <v>0.54878048780487809</v>
+        <v>0.48780487804878048</v>
       </c>
       <c r="Z6">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="AA6">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="AB6">
-        <v>17</v>
+        <v>40</v>
       </c>
       <c r="AC6" s="2">
-        <v>0.50262644454449945</v>
+        <v>0.49452198709290113</v>
       </c>
       <c r="AD6" s="2">
-        <v>0.8341561938958707</v>
+        <v>0.69838420107719923</v>
       </c>
       <c r="AE6" s="2">
-        <v>0.81754278728606355</v>
+        <v>0.86485612673779499</v>
       </c>
       <c r="AF6" s="2">
-        <v>0.65362811791383224</v>
+        <v>0.81225783726664313</v>
       </c>
       <c r="AG6" s="2">
-        <v>0.62869348522605906</v>
+        <v>0.45386790028270368</v>
       </c>
       <c r="AH6" s="2">
-        <v>0.906240668856375</v>
+        <v>0.80485584218512896</v>
       </c>
       <c r="AI6" s="2">
-        <v>0</v>
+        <v>0.54719271623672228</v>
       </c>
       <c r="AJ6" s="2">
-        <v>0.1111111111111111</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="AK6" s="2">
-        <v>0.75609756097560976</v>
+        <v>0.97560975609756095</v>
       </c>
       <c r="AL6" s="2">
-        <v>0.45161290322580638</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:38" x14ac:dyDescent="0.35">
       <c r="A7" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B7">
-        <v>2210</v>
+        <v>3349</v>
       </c>
       <c r="C7">
-        <v>1990</v>
+        <v>2809</v>
       </c>
       <c r="D7">
-        <v>2066</v>
+        <v>3035</v>
       </c>
       <c r="E7">
-        <v>223</v>
+        <v>872</v>
       </c>
       <c r="F7">
         <v>0</v>
       </c>
       <c r="G7">
-        <v>2288</v>
+        <v>3717</v>
       </c>
       <c r="H7">
-        <v>108</v>
+        <v>634</v>
       </c>
       <c r="I7" s="2">
-        <v>0.90045248868778283</v>
+        <v>0.83875783816064498</v>
       </c>
       <c r="J7">
-        <v>2288</v>
+        <v>3717</v>
       </c>
       <c r="K7">
         <v>1</v>
       </c>
       <c r="L7">
-        <v>2210</v>
+        <v>3333</v>
       </c>
       <c r="M7" s="2">
-        <v>0.5210859728506787</v>
+        <v>0.38655865586558658</v>
       </c>
       <c r="N7" s="2">
-        <v>0.17405959377925789</v>
+        <v>0.20751680437521461</v>
       </c>
       <c r="O7" s="2">
-        <v>0.30419448593104059</v>
+        <v>0.27465749868410411</v>
       </c>
       <c r="P7" s="2">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="Q7" s="2">
-        <v>0.12593255744553861</v>
+        <v>0.10231696014828549</v>
       </c>
       <c r="R7" s="2">
-        <v>0.1342764954082899</v>
+        <v>0.11018078020932449</v>
       </c>
       <c r="S7" s="2">
-        <v>0.37555720653788999</v>
+        <v>0.34629294755877033</v>
       </c>
       <c r="T7" s="2">
         <v>0</v>
       </c>
       <c r="U7">
-        <v>1098</v>
+        <v>3272</v>
       </c>
       <c r="V7">
-        <v>2264</v>
+        <v>3528</v>
       </c>
       <c r="W7" s="2">
-        <v>0.58059664897300767</v>
+        <v>0.55572812751818845</v>
       </c>
       <c r="X7" s="2">
-        <v>0</v>
+        <v>1.7182906095825321E-2</v>
       </c>
       <c r="Y7" s="2">
-        <v>0.40243902439024393</v>
+        <v>0.54878048780487809</v>
       </c>
       <c r="Z7">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA7">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="AB7">
-        <v>31</v>
+        <v>17</v>
       </c>
       <c r="AC7" s="2">
-        <v>0.33168242533393372</v>
+        <v>0.50262644454449945</v>
       </c>
       <c r="AD7" s="2">
-        <v>0.51346499102333931</v>
+        <v>0.8341561938958707</v>
       </c>
       <c r="AE7" s="2">
-        <v>0.41046728971962609</v>
+        <v>0.81754278728606355</v>
       </c>
       <c r="AF7" s="2">
-        <v>0.98178664353859502</v>
+        <v>0.65362811791383224</v>
       </c>
       <c r="AG7" s="2">
-        <v>0.88743718592964826</v>
+        <v>0.62869348522605906</v>
       </c>
       <c r="AH7" s="2">
-        <v>0.93484162895927603</v>
+        <v>0.906240668856375</v>
       </c>
       <c r="AI7" s="2">
         <v>0</v>
@@ -3023,357 +3142,473 @@
         <v>0.1111111111111111</v>
       </c>
       <c r="AK7" s="2">
-        <v>0.78048780487804881</v>
+        <v>0.75609756097560976</v>
       </c>
       <c r="AL7" s="2">
-        <v>3.125E-2</v>
+        <v>0.45161290322580638</v>
       </c>
     </row>
     <row r="8" spans="1:38" x14ac:dyDescent="0.35">
       <c r="A8" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B8">
-        <v>1756</v>
+        <v>2210</v>
       </c>
       <c r="C8">
-        <v>2275</v>
+        <v>1990</v>
       </c>
       <c r="D8">
-        <v>1756</v>
+        <v>2066</v>
       </c>
       <c r="E8">
-        <v>669</v>
+        <v>223</v>
       </c>
       <c r="F8">
-        <v>231</v>
+        <v>0</v>
       </c>
       <c r="G8">
-        <v>2127</v>
+        <v>2288</v>
       </c>
       <c r="H8">
-        <v>519</v>
+        <v>108</v>
       </c>
       <c r="I8" s="2">
-        <v>1.295558086560364</v>
+        <v>0.90045248868778283</v>
       </c>
       <c r="J8">
-        <v>2127</v>
+        <v>2288</v>
       </c>
       <c r="K8">
         <v>1</v>
       </c>
       <c r="L8">
-        <v>1740</v>
+        <v>2210</v>
       </c>
       <c r="M8" s="2">
-        <v>0.4707681525091113</v>
+        <v>0.5210859728506787</v>
       </c>
       <c r="N8" s="2">
-        <v>0.19736798734305341</v>
+        <v>0.17405959377925789</v>
       </c>
       <c r="O8" s="2">
-        <v>0.29989304928032512</v>
+        <v>0.30419448593104059</v>
       </c>
       <c r="P8" s="2">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="Q8" s="2">
-        <v>4.8730064973419973E-2</v>
+        <v>0.12593255744553861</v>
       </c>
       <c r="R8" s="2">
-        <v>9.4193869922751056E-2</v>
+        <v>0.1342764954082899</v>
       </c>
       <c r="S8" s="2">
-        <v>0.33479729729729729</v>
+        <v>0.37555720653788999</v>
       </c>
       <c r="T8" s="2">
         <v>0</v>
       </c>
       <c r="U8">
-        <v>876</v>
+        <v>1098</v>
       </c>
       <c r="V8">
-        <v>2085</v>
+        <v>2264</v>
       </c>
       <c r="W8" s="2">
-        <v>0.62640319375613496</v>
+        <v>0.58059664897300767</v>
       </c>
       <c r="X8" s="2">
         <v>0</v>
       </c>
       <c r="Y8" s="2">
-        <v>0.6097560975609756</v>
+        <v>0.40243902439024393</v>
       </c>
       <c r="Z8">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="AA8">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="AB8">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="AC8" s="2">
-        <v>0.26354494972234732</v>
+        <v>0.33168242533393372</v>
       </c>
       <c r="AD8" s="2">
-        <v>0.47733393177737882</v>
+        <v>0.51346499102333931</v>
       </c>
       <c r="AE8" s="2">
-        <v>0.32747663551401868</v>
+        <v>0.41046728971962609</v>
       </c>
       <c r="AF8" s="2">
-        <v>0.90416305290546406</v>
+        <v>0.98178664353859502</v>
       </c>
       <c r="AG8" s="2">
-        <v>0.77626373626373624</v>
+        <v>0.88743718592964826</v>
       </c>
       <c r="AH8" s="2">
-        <v>1</v>
+        <v>0.93484162895927603</v>
       </c>
       <c r="AI8" s="2">
-        <v>0.1315489749430524</v>
+        <v>0</v>
       </c>
       <c r="AJ8" s="2">
         <v>0.1111111111111111</v>
       </c>
       <c r="AK8" s="2">
-        <v>0.92682926829268297</v>
+        <v>0.78048780487804881</v>
       </c>
       <c r="AL8" s="2">
-        <v>0.31578947368421051</v>
+        <v>3.125E-2</v>
       </c>
     </row>
     <row r="9" spans="1:38" x14ac:dyDescent="0.35">
       <c r="A9" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B9">
-        <v>1509</v>
+        <v>1756</v>
       </c>
       <c r="C9">
-        <v>1625</v>
+        <v>2275</v>
       </c>
       <c r="D9">
-        <v>1413</v>
+        <v>1756</v>
       </c>
       <c r="E9">
-        <v>137</v>
+        <v>669</v>
       </c>
       <c r="F9">
-        <v>701</v>
+        <v>231</v>
       </c>
       <c r="G9">
-        <v>1561</v>
+        <v>2127</v>
       </c>
       <c r="H9">
-        <v>130</v>
+        <v>519</v>
       </c>
       <c r="I9" s="2">
-        <v>1.0768721007289599</v>
+        <v>1.295558086560364</v>
       </c>
       <c r="J9">
-        <v>1596</v>
+        <v>2127</v>
       </c>
       <c r="K9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L9">
-        <v>1428</v>
+        <v>1740</v>
       </c>
       <c r="M9" s="2">
-        <v>0.65799763846555182</v>
+        <v>0.4707681525091113</v>
       </c>
       <c r="N9" s="2">
-        <v>9.3261369543806497E-2</v>
+        <v>0.19736798734305341</v>
       </c>
       <c r="O9" s="2">
-        <v>0.30503747038946089</v>
+        <v>0.29989304928032512</v>
       </c>
       <c r="P9" s="2">
-        <v>2</v>
+        <v>0.2</v>
       </c>
       <c r="Q9" s="2">
-        <v>0.1349693251533742</v>
+        <v>4.8730064973419973E-2</v>
       </c>
       <c r="R9" s="2">
-        <v>0.11541799247902811</v>
+        <v>9.4193869922751056E-2</v>
       </c>
       <c r="S9" s="2">
-        <v>0</v>
+        <v>0.33479729729729729</v>
       </c>
       <c r="T9" s="2">
-        <v>0.22222222222222221</v>
+        <v>0</v>
       </c>
       <c r="U9">
-        <v>1395</v>
+        <v>876</v>
       </c>
       <c r="V9">
-        <v>1550</v>
+        <v>2085</v>
       </c>
       <c r="W9" s="2">
-        <v>0</v>
+        <v>0.62640319375613496</v>
       </c>
       <c r="X9" s="2">
-        <v>-4.1642145093303717E-2</v>
+        <v>0</v>
       </c>
       <c r="Y9" s="2">
-        <v>0.64634146341463417</v>
+        <v>0.6097560975609756</v>
       </c>
       <c r="Z9">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="AA9">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="AB9">
-        <v>3</v>
+        <v>26</v>
       </c>
       <c r="AC9" s="2">
-        <v>0.2264745610085547</v>
+        <v>0.26354494972234732</v>
       </c>
       <c r="AD9" s="2">
-        <v>0.35816876122082592</v>
+        <v>0.47733393177737882</v>
       </c>
       <c r="AE9" s="2">
-        <v>0.52149532710280377</v>
+        <v>0.32747663551401868</v>
       </c>
       <c r="AF9" s="2">
-        <v>0.67215958369470941</v>
+        <v>0.90416305290546406</v>
       </c>
       <c r="AG9" s="2">
-        <v>0.92015855039637595</v>
+        <v>0.77626373626373624</v>
       </c>
       <c r="AH9" s="2">
-        <v>0.93638170974155066</v>
+        <v>1</v>
       </c>
       <c r="AI9" s="2">
-        <v>0.46454605699138501</v>
+        <v>0.1315489749430524</v>
       </c>
       <c r="AJ9" s="2">
-        <v>0.22222222222222221</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="AK9" s="2">
-        <v>0.68292682926829273</v>
+        <v>0.92682926829268297</v>
       </c>
       <c r="AL9" s="2">
-        <v>0.8928571428571429</v>
+        <v>0.31578947368421051</v>
       </c>
     </row>
     <row r="10" spans="1:38" x14ac:dyDescent="0.35">
       <c r="A10" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B10">
+        <v>1509</v>
+      </c>
+      <c r="C10">
+        <v>1625</v>
+      </c>
+      <c r="D10">
+        <v>1413</v>
+      </c>
+      <c r="E10">
+        <v>137</v>
+      </c>
+      <c r="F10">
+        <v>701</v>
+      </c>
+      <c r="G10">
+        <v>1561</v>
+      </c>
+      <c r="H10">
+        <v>130</v>
+      </c>
+      <c r="I10" s="2">
+        <v>1.0768721007289599</v>
+      </c>
+      <c r="J10">
+        <v>1596</v>
+      </c>
+      <c r="K10">
+        <v>2</v>
+      </c>
+      <c r="L10">
+        <v>1428</v>
+      </c>
+      <c r="M10" s="2">
+        <v>0.65799763846555182</v>
+      </c>
+      <c r="N10" s="2">
+        <v>9.3261369543806497E-2</v>
+      </c>
+      <c r="O10" s="2">
+        <v>0.30503747038946089</v>
+      </c>
+      <c r="P10" s="2">
+        <v>2</v>
+      </c>
+      <c r="Q10" s="2">
+        <v>0.1349693251533742</v>
+      </c>
+      <c r="R10" s="2">
+        <v>0.11541799247902811</v>
+      </c>
+      <c r="S10" s="2">
+        <v>0</v>
+      </c>
+      <c r="T10" s="2">
+        <v>0.22222222222222221</v>
+      </c>
+      <c r="U10">
+        <v>1395</v>
+      </c>
+      <c r="V10">
+        <v>1550</v>
+      </c>
+      <c r="W10" s="2">
+        <v>0</v>
+      </c>
+      <c r="X10" s="2">
+        <v>-4.1642145093303717E-2</v>
+      </c>
+      <c r="Y10" s="2">
+        <v>0.64634146341463417</v>
+      </c>
+      <c r="Z10">
+        <v>13</v>
+      </c>
+      <c r="AA10">
+        <v>25</v>
+      </c>
+      <c r="AB10">
+        <v>3</v>
+      </c>
+      <c r="AC10" s="2">
+        <v>0.2264745610085547</v>
+      </c>
+      <c r="AD10" s="2">
+        <v>0.35816876122082592</v>
+      </c>
+      <c r="AE10" s="2">
+        <v>0.52149532710280377</v>
+      </c>
+      <c r="AF10" s="2">
+        <v>0.67215958369470941</v>
+      </c>
+      <c r="AG10" s="2">
+        <v>0.92015855039637595</v>
+      </c>
+      <c r="AH10" s="2">
+        <v>0.93638170974155066</v>
+      </c>
+      <c r="AI10" s="2">
+        <v>0.46454605699138501</v>
+      </c>
+      <c r="AJ10" s="2">
+        <v>0.22222222222222221</v>
+      </c>
+      <c r="AK10" s="2">
+        <v>0.68292682926829273</v>
+      </c>
+      <c r="AL10" s="2">
+        <v>0.8928571428571429</v>
+      </c>
+    </row>
+    <row r="11" spans="1:38" x14ac:dyDescent="0.35">
+      <c r="A11" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="B10">
+      <c r="B11">
         <v>6663</v>
       </c>
-      <c r="C10">
+      <c r="C11">
         <v>1766</v>
       </c>
-      <c r="D10">
+      <c r="D11">
         <v>3871</v>
       </c>
-      <c r="E10">
+      <c r="E11">
         <v>284</v>
       </c>
-      <c r="F10">
+      <c r="F11">
         <v>5151</v>
       </c>
-      <c r="G10">
+      <c r="G11">
         <v>2341</v>
       </c>
-      <c r="H10">
+      <c r="H11">
         <v>201</v>
       </c>
-      <c r="I10" s="2">
+      <c r="I11" s="2">
         <v>0.26504577517634698</v>
       </c>
-      <c r="J10">
+      <c r="J11">
         <v>4456</v>
       </c>
-      <c r="K10">
+      <c r="K11">
         <v>9</v>
       </c>
-      <c r="L10">
+      <c r="L11">
         <v>3560</v>
       </c>
-      <c r="M10" s="2">
+      <c r="M11" s="2">
         <v>0.70230568158297135</v>
       </c>
-      <c r="N10" s="2">
+      <c r="N11" s="2">
         <v>0.26039882917555451</v>
       </c>
-      <c r="O10" s="2">
+      <c r="O11" s="2">
         <v>0.42611389882833578</v>
       </c>
-      <c r="P10" s="2">
-        <v>0</v>
-      </c>
-      <c r="Q10" s="2">
-        <v>1</v>
-      </c>
-      <c r="R10" s="2">
-        <v>1</v>
-      </c>
-      <c r="S10" s="2">
-        <v>1</v>
-      </c>
-      <c r="T10" s="2">
-        <v>1</v>
-      </c>
-      <c r="U10">
+      <c r="P11" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q11" s="2">
+        <v>1</v>
+      </c>
+      <c r="R11" s="2">
+        <v>1</v>
+      </c>
+      <c r="S11" s="2">
+        <v>1</v>
+      </c>
+      <c r="T11" s="2">
+        <v>1</v>
+      </c>
+      <c r="U11">
         <v>2675</v>
       </c>
-      <c r="V10">
+      <c r="V11">
         <v>2306</v>
       </c>
-      <c r="W10" s="2">
-        <v>1</v>
-      </c>
-      <c r="X10" s="2">
-        <v>1</v>
-      </c>
-      <c r="Y10" s="2">
-        <v>1</v>
-      </c>
-      <c r="Z10">
-        <v>0</v>
-      </c>
-      <c r="AA10">
+      <c r="W11" s="2">
+        <v>1</v>
+      </c>
+      <c r="X11" s="2">
+        <v>1</v>
+      </c>
+      <c r="Y11" s="2">
+        <v>1</v>
+      </c>
+      <c r="Z11">
+        <v>0</v>
+      </c>
+      <c r="AA11">
         <v>41</v>
       </c>
-      <c r="AB10">
-        <v>0</v>
-      </c>
-      <c r="AC10" s="2">
-        <v>1</v>
-      </c>
-      <c r="AD10" s="2">
-        <v>1</v>
-      </c>
-      <c r="AE10" s="2">
-        <v>1</v>
-      </c>
-      <c r="AF10" s="2">
-        <v>1</v>
-      </c>
-      <c r="AG10" s="2">
-        <v>1</v>
-      </c>
-      <c r="AH10" s="2">
+      <c r="AB11">
+        <v>0</v>
+      </c>
+      <c r="AC11" s="2">
+        <v>1</v>
+      </c>
+      <c r="AD11" s="2">
+        <v>1</v>
+      </c>
+      <c r="AE11" s="2">
+        <v>1</v>
+      </c>
+      <c r="AF11" s="2">
+        <v>1</v>
+      </c>
+      <c r="AG11" s="2">
+        <v>1</v>
+      </c>
+      <c r="AH11" s="2">
         <v>0.58096953324328382</v>
       </c>
-      <c r="AI10" s="2">
+      <c r="AI11" s="2">
         <v>0.77307519135524538</v>
       </c>
-      <c r="AJ10" s="2">
-        <v>1</v>
-      </c>
-      <c r="AK10" s="2">
-        <v>1</v>
-      </c>
-      <c r="AL10" s="2">
+      <c r="AJ11" s="2">
+        <v>1</v>
+      </c>
+      <c r="AK11" s="2">
+        <v>1</v>
+      </c>
+      <c r="AL11" s="2">
         <v>1</v>
       </c>
     </row>
@@ -3384,7 +3619,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:AL10"/>
+  <dimension ref="A1:AL11"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="17" customWidth="1"/>
@@ -3888,338 +4123,338 @@
     </row>
     <row r="5" spans="1:38" x14ac:dyDescent="0.35">
       <c r="A5" s="1" t="s">
-        <v>40</v>
+        <v>85</v>
       </c>
       <c r="B5">
-        <v>2669</v>
+        <v>1121</v>
       </c>
       <c r="C5">
-        <v>2309</v>
+        <v>728</v>
       </c>
       <c r="D5">
-        <v>2250</v>
+        <v>1101</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>115</v>
       </c>
       <c r="F5">
-        <v>1337</v>
+        <v>726</v>
       </c>
       <c r="G5">
-        <v>2594</v>
+        <v>529</v>
       </c>
       <c r="H5">
-        <v>0</v>
+        <v>98</v>
       </c>
       <c r="I5" s="2">
-        <v>0.8651180217309854</v>
+        <v>0.64942016057091878</v>
       </c>
       <c r="J5">
-        <v>2726</v>
+        <v>1179</v>
       </c>
       <c r="K5">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="L5">
-        <v>2611</v>
+        <v>1101</v>
       </c>
       <c r="M5" s="2">
-        <v>0.74282250599909816</v>
+        <v>0.54291371480472306</v>
       </c>
       <c r="N5" s="2">
-        <v>0.34529093438195768</v>
+        <v>0.30050928554050771</v>
       </c>
       <c r="O5" s="2">
-        <v>0.49436527373838529</v>
+        <v>0.39141094651458852</v>
       </c>
       <c r="P5">
-        <v>4</v>
+        <v>0.2</v>
       </c>
       <c r="Q5" s="2">
-        <v>0.24846796657381609</v>
+        <v>0.12994093593820991</v>
       </c>
       <c r="R5" s="2">
-        <v>0.21067783302800311</v>
+        <v>0.1086303134392443</v>
       </c>
       <c r="S5" s="2">
-        <v>0.31569246972090581</v>
+        <v>0.12743628185907049</v>
       </c>
       <c r="T5" s="2">
-        <v>0.33333333333333331</v>
+        <v>0.41666666666666669</v>
       </c>
       <c r="U5">
-        <v>2627</v>
+        <v>632</v>
       </c>
       <c r="V5">
-        <v>2554</v>
+        <v>510</v>
       </c>
       <c r="W5" s="2">
-        <v>0.34777878912070093</v>
+        <v>0.23406533553592379</v>
       </c>
       <c r="X5" s="2">
-        <v>0.2433487667665569</v>
+        <v>0</v>
       </c>
       <c r="Y5" s="2">
-        <v>0.5</v>
+        <v>0.56666666666666665</v>
       </c>
       <c r="Z5">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AA5">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="AB5">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="AC5" s="2">
-        <v>0.75121768452603976</v>
+        <v>0.55910224438902745</v>
       </c>
       <c r="AD5" s="2">
-        <v>0.80924431401320618</v>
+        <v>0.53445149592021757</v>
       </c>
       <c r="AE5" s="2">
-        <v>0.70612866387514273</v>
+        <v>0.34070080862533692</v>
       </c>
       <c r="AF5" s="2">
-        <v>0.81127642913077525</v>
+        <v>0.24613899613899609</v>
       </c>
       <c r="AG5" s="2">
-        <v>0.98787353832828062</v>
+        <v>0.31915826391933361</v>
       </c>
       <c r="AH5" s="2">
-        <v>0.84301236418134129</v>
+        <v>0.98215878679750224</v>
       </c>
       <c r="AI5" s="2">
-        <v>0.5009366804046459</v>
+        <v>0.64763603925066904</v>
       </c>
       <c r="AJ5" s="2">
-        <v>0.42857142857142849</v>
+        <v>0.63636363636363635</v>
       </c>
       <c r="AK5" s="2">
-        <v>1</v>
+        <v>0.56666666666666665</v>
       </c>
       <c r="AL5" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:38" x14ac:dyDescent="0.35">
       <c r="A6" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B6">
-        <v>2503</v>
+        <v>2669</v>
       </c>
       <c r="C6">
-        <v>1700</v>
+        <v>2309</v>
       </c>
       <c r="D6">
-        <v>2360</v>
+        <v>2250</v>
       </c>
       <c r="E6">
-        <v>734</v>
+        <v>0</v>
       </c>
       <c r="F6">
-        <v>0</v>
+        <v>1337</v>
       </c>
       <c r="G6">
-        <v>3043</v>
+        <v>2594</v>
       </c>
       <c r="H6">
-        <v>646</v>
+        <v>0</v>
       </c>
       <c r="I6" s="2">
-        <v>0.67918497802636835</v>
+        <v>0.8651180217309854</v>
       </c>
       <c r="J6">
-        <v>3043</v>
+        <v>2726</v>
       </c>
       <c r="K6">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L6">
-        <v>2494</v>
+        <v>2611</v>
       </c>
       <c r="M6" s="2">
-        <v>0.40024057738572583</v>
+        <v>0.74282250599909816</v>
       </c>
       <c r="N6" s="2">
-        <v>0.20752934711708421</v>
+        <v>0.34529093438195768</v>
       </c>
       <c r="O6" s="2">
-        <v>0.27979605846782479</v>
+        <v>0.49436527373838529</v>
       </c>
       <c r="P6">
-        <v>1.2</v>
+        <v>4</v>
       </c>
       <c r="Q6" s="2">
-        <v>0.1973244147157191</v>
+        <v>0.24846796657381609</v>
       </c>
       <c r="R6" s="2">
-        <v>0.20268972142170991</v>
+        <v>0.21067783302800311</v>
       </c>
       <c r="S6" s="2">
-        <v>0.36115902035184538</v>
+        <v>0.31569246972090581</v>
       </c>
       <c r="T6" s="2">
-        <v>0</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="U6">
-        <v>2441</v>
+        <v>2627</v>
       </c>
       <c r="V6">
-        <v>2936</v>
+        <v>2554</v>
       </c>
       <c r="W6" s="2">
-        <v>0.41856272206575118</v>
+        <v>0.34777878912070093</v>
       </c>
       <c r="X6" s="2">
-        <v>0.31182225583801559</v>
+        <v>0.2433487667665569</v>
       </c>
       <c r="Y6" s="2">
-        <v>0.9</v>
+        <v>0.5</v>
       </c>
       <c r="Z6">
         <v>0</v>
       </c>
       <c r="AA6">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="AB6">
-        <v>6</v>
+        <v>30</v>
       </c>
       <c r="AC6" s="2">
-        <v>0.801038753495805</v>
+        <v>0.75121768452603976</v>
       </c>
       <c r="AD6" s="2">
-        <v>0.72494249096286556</v>
+        <v>0.80924431401320618</v>
       </c>
       <c r="AE6" s="2">
-        <v>0.75993445309299468</v>
+        <v>0.70612866387514273</v>
       </c>
       <c r="AF6" s="2">
-        <v>0.70572207084468663</v>
+        <v>0.81127642913077525</v>
       </c>
       <c r="AG6" s="2">
-        <v>0.74528715475668561</v>
+        <v>0.98787353832828062</v>
       </c>
       <c r="AH6" s="2">
-        <v>0.94286855773072309</v>
+        <v>0.84301236418134129</v>
       </c>
       <c r="AI6" s="2">
-        <v>0</v>
+        <v>0.5009366804046459</v>
       </c>
       <c r="AJ6" s="2">
-        <v>0.14285714285714279</v>
+        <v>0.42857142857142849</v>
       </c>
       <c r="AK6" s="2">
         <v>1</v>
       </c>
       <c r="AL6" s="2">
-        <v>0.8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:38" x14ac:dyDescent="0.35">
       <c r="A7" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B7">
-        <v>1710</v>
+        <v>2503</v>
       </c>
       <c r="C7">
-        <v>1141</v>
+        <v>1700</v>
       </c>
       <c r="D7">
-        <v>1567</v>
+        <v>2360</v>
       </c>
       <c r="E7">
-        <v>149</v>
+        <v>734</v>
       </c>
       <c r="F7">
         <v>0</v>
       </c>
       <c r="G7">
-        <v>1928</v>
+        <v>3043</v>
       </c>
       <c r="H7">
-        <v>116</v>
+        <v>646</v>
       </c>
       <c r="I7" s="2">
-        <v>0.6672514619883041</v>
+        <v>0.67918497802636835</v>
       </c>
       <c r="J7">
-        <v>1928</v>
+        <v>3043</v>
       </c>
       <c r="K7">
         <v>1</v>
       </c>
       <c r="L7">
-        <v>1710</v>
+        <v>2494</v>
       </c>
       <c r="M7" s="2">
-        <v>0.53005847953216378</v>
+        <v>0.40024057738572583</v>
       </c>
       <c r="N7" s="2">
-        <v>0.17622627047311479</v>
+        <v>0.20752934711708421</v>
       </c>
       <c r="O7" s="2">
-        <v>0.30891334887025812</v>
+        <v>0.27979605846782479</v>
       </c>
       <c r="P7">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="Q7" s="2">
-        <v>0.116384647131655</v>
+        <v>0.1973244147157191</v>
       </c>
       <c r="R7" s="2">
-        <v>0.13983414355161569</v>
+        <v>0.20268972142170991</v>
       </c>
       <c r="S7" s="2">
-        <v>0.30219146482122261</v>
+        <v>0.36115902035184538</v>
       </c>
       <c r="T7" s="2">
         <v>0</v>
       </c>
       <c r="U7">
-        <v>850</v>
+        <v>2441</v>
       </c>
       <c r="V7">
-        <v>1914</v>
+        <v>2936</v>
       </c>
       <c r="W7" s="2">
-        <v>0.42042321477805339</v>
+        <v>0.41856272206575118</v>
       </c>
       <c r="X7" s="2">
-        <v>0</v>
+        <v>0.31182225583801559</v>
       </c>
       <c r="Y7" s="2">
-        <v>0.33333333333333331</v>
+        <v>0.9</v>
       </c>
       <c r="Z7">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AA7">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AB7">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="AC7" s="2">
-        <v>0.8528678304239401</v>
+        <v>0.801038753495805</v>
       </c>
       <c r="AD7" s="2">
-        <v>0.8739800543970988</v>
+        <v>0.72494249096286556</v>
       </c>
       <c r="AE7" s="2">
-        <v>0.4582210242587601</v>
+        <v>0.75993445309299468</v>
       </c>
       <c r="AF7" s="2">
-        <v>0.92374517374517373</v>
+        <v>0.70572207084468663</v>
       </c>
       <c r="AG7" s="2">
-        <v>0.50021920210434023</v>
+        <v>0.74528715475668561</v>
       </c>
       <c r="AH7" s="2">
-        <v>0.91637426900584795</v>
+        <v>0.94286855773072309</v>
       </c>
       <c r="AI7" s="2">
         <v>0</v>
@@ -4228,357 +4463,473 @@
         <v>0.14285714285714279</v>
       </c>
       <c r="AK7" s="2">
-        <v>0.66666666666666663</v>
+        <v>1</v>
       </c>
       <c r="AL7" s="2">
-        <v>0</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="8" spans="1:38" x14ac:dyDescent="0.35">
       <c r="A8" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B8">
-        <v>1322</v>
+        <v>1710</v>
       </c>
       <c r="C8">
-        <v>1428</v>
+        <v>1141</v>
       </c>
       <c r="D8">
-        <v>1322</v>
+        <v>1567</v>
       </c>
       <c r="E8">
-        <v>570</v>
+        <v>149</v>
       </c>
       <c r="F8">
-        <v>112</v>
+        <v>0</v>
       </c>
       <c r="G8">
-        <v>1789</v>
+        <v>1928</v>
       </c>
       <c r="H8">
-        <v>545</v>
+        <v>116</v>
       </c>
       <c r="I8" s="2">
-        <v>1.0801815431164901</v>
+        <v>0.6672514619883041</v>
       </c>
       <c r="J8">
-        <v>1789</v>
+        <v>1928</v>
       </c>
       <c r="K8">
         <v>1</v>
       </c>
       <c r="L8">
-        <v>1313</v>
+        <v>1710</v>
       </c>
       <c r="M8" s="2">
-        <v>0.53667038407137413</v>
+        <v>0.53005847953216378</v>
       </c>
       <c r="N8" s="2">
-        <v>0.19933036322857331</v>
+        <v>0.17622627047311479</v>
       </c>
       <c r="O8" s="2">
-        <v>0.32583287104462361</v>
+        <v>0.30891334887025812</v>
       </c>
       <c r="P8">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="Q8" s="2">
-        <v>0.10223782360684509</v>
+        <v>0.116384647131655</v>
       </c>
       <c r="R8" s="2">
-        <v>0.2099621689785624</v>
+        <v>0.13983414355161569</v>
       </c>
       <c r="S8" s="2">
-        <v>0.32875226039783001</v>
+        <v>0.30219146482122261</v>
       </c>
       <c r="T8" s="2">
         <v>0</v>
       </c>
       <c r="U8">
-        <v>657</v>
+        <v>850</v>
       </c>
       <c r="V8">
-        <v>1766</v>
+        <v>1914</v>
       </c>
       <c r="W8" s="2">
-        <v>0.42500140097227468</v>
+        <v>0.42042321477805339</v>
       </c>
       <c r="X8" s="2">
         <v>0</v>
       </c>
       <c r="Y8" s="2">
-        <v>0.6166666666666667</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="Z8">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AA8">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="AB8">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="AC8" s="2">
-        <v>0.65935162094763089</v>
+        <v>0.8528678304239401</v>
       </c>
       <c r="AD8" s="2">
-        <v>0.81097008159564821</v>
+        <v>0.8739800543970988</v>
       </c>
       <c r="AE8" s="2">
-        <v>0.35417789757412399</v>
+        <v>0.4582210242587601</v>
       </c>
       <c r="AF8" s="2">
-        <v>0.85231660231660233</v>
+        <v>0.92374517374517373</v>
       </c>
       <c r="AG8" s="2">
-        <v>0.62604120999561597</v>
+        <v>0.50021920210434023</v>
       </c>
       <c r="AH8" s="2">
-        <v>1</v>
+        <v>0.91637426900584795</v>
       </c>
       <c r="AI8" s="2">
-        <v>8.4720121028744322E-2</v>
+        <v>0</v>
       </c>
       <c r="AJ8" s="2">
         <v>0.14285714285714279</v>
       </c>
       <c r="AK8" s="2">
-        <v>1</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="AL8" s="2">
-        <v>0.23333333333333331</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:38" x14ac:dyDescent="0.35">
       <c r="A9" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B9">
-        <v>1601</v>
+        <v>1322</v>
       </c>
       <c r="C9">
-        <v>1879</v>
+        <v>1428</v>
       </c>
       <c r="D9">
-        <v>1523</v>
+        <v>1322</v>
       </c>
       <c r="E9">
-        <v>147</v>
+        <v>570</v>
       </c>
       <c r="F9">
-        <v>721</v>
+        <v>112</v>
       </c>
       <c r="G9">
-        <v>1677</v>
+        <v>1789</v>
       </c>
       <c r="H9">
-        <v>129</v>
+        <v>545</v>
       </c>
       <c r="I9" s="2">
-        <v>1.1736414740787009</v>
+        <v>1.0801815431164901</v>
       </c>
       <c r="J9">
-        <v>1712</v>
+        <v>1789</v>
       </c>
       <c r="K9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L9">
-        <v>1524</v>
+        <v>1313</v>
       </c>
       <c r="M9" s="2">
-        <v>0.65490126457815534</v>
+        <v>0.53667038407137413</v>
       </c>
       <c r="N9" s="2">
-        <v>9.3285486641637799E-2</v>
+        <v>0.19933036322857331</v>
       </c>
       <c r="O9" s="2">
-        <v>0.30389140336783188</v>
+        <v>0.32583287104462361</v>
       </c>
       <c r="P9">
-        <v>2</v>
+        <v>0.2</v>
       </c>
       <c r="Q9" s="2">
-        <v>0.1227775914122778</v>
+        <v>0.10223782360684509</v>
       </c>
       <c r="R9" s="2">
-        <v>0.14045801526717561</v>
+        <v>0.2099621689785624</v>
       </c>
       <c r="S9" s="2">
-        <v>0</v>
+        <v>0.32875226039783001</v>
       </c>
       <c r="T9" s="2">
-        <v>0.33333333333333331</v>
+        <v>0</v>
       </c>
       <c r="U9">
-        <v>1492</v>
+        <v>657</v>
       </c>
       <c r="V9">
-        <v>1663</v>
+        <v>1766</v>
       </c>
       <c r="W9" s="2">
-        <v>0</v>
+        <v>0.42500140097227468</v>
       </c>
       <c r="X9" s="2">
-        <v>-1.7288123177163911E-2</v>
+        <v>0</v>
       </c>
       <c r="Y9" s="2">
-        <v>0.66666666666666663</v>
+        <v>0.6166666666666667</v>
       </c>
       <c r="Z9">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="AA9">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="AB9">
-        <v>2</v>
+        <v>23</v>
       </c>
       <c r="AC9" s="2">
-        <v>0.79850374064837903</v>
+        <v>0.65935162094763089</v>
       </c>
       <c r="AD9" s="2">
-        <v>0.7760652765185857</v>
+        <v>0.81097008159564821</v>
       </c>
       <c r="AE9" s="2">
-        <v>0.80431266846361182</v>
+        <v>0.35417789757412399</v>
       </c>
       <c r="AF9" s="2">
-        <v>0.80260617760617758</v>
+        <v>0.85231660231660233</v>
       </c>
       <c r="AG9" s="2">
-        <v>0.82376150811047788</v>
+        <v>0.62604120999561597</v>
       </c>
       <c r="AH9" s="2">
-        <v>0.95128044971892567</v>
+        <v>1</v>
       </c>
       <c r="AI9" s="2">
-        <v>0.45034353529044352</v>
+        <v>8.4720121028744322E-2</v>
       </c>
       <c r="AJ9" s="2">
-        <v>0.2857142857142857</v>
+        <v>0.14285714285714279</v>
       </c>
       <c r="AK9" s="2">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="AL9" s="2">
-        <v>0.90476190476190477</v>
+        <v>0.23333333333333331</v>
       </c>
     </row>
     <row r="10" spans="1:38" x14ac:dyDescent="0.35">
       <c r="A10" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B10">
+        <v>1601</v>
+      </c>
+      <c r="C10">
+        <v>1879</v>
+      </c>
+      <c r="D10">
+        <v>1523</v>
+      </c>
+      <c r="E10">
+        <v>147</v>
+      </c>
+      <c r="F10">
+        <v>721</v>
+      </c>
+      <c r="G10">
+        <v>1677</v>
+      </c>
+      <c r="H10">
+        <v>129</v>
+      </c>
+      <c r="I10" s="2">
+        <v>1.1736414740787009</v>
+      </c>
+      <c r="J10">
+        <v>1712</v>
+      </c>
+      <c r="K10">
+        <v>2</v>
+      </c>
+      <c r="L10">
+        <v>1524</v>
+      </c>
+      <c r="M10" s="2">
+        <v>0.65490126457815534</v>
+      </c>
+      <c r="N10" s="2">
+        <v>9.3285486641637799E-2</v>
+      </c>
+      <c r="O10" s="2">
+        <v>0.30389140336783188</v>
+      </c>
+      <c r="P10">
+        <v>2</v>
+      </c>
+      <c r="Q10" s="2">
+        <v>0.1227775914122778</v>
+      </c>
+      <c r="R10" s="2">
+        <v>0.14045801526717561</v>
+      </c>
+      <c r="S10" s="2">
+        <v>0</v>
+      </c>
+      <c r="T10" s="2">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="U10">
+        <v>1492</v>
+      </c>
+      <c r="V10">
+        <v>1663</v>
+      </c>
+      <c r="W10" s="2">
+        <v>0</v>
+      </c>
+      <c r="X10" s="2">
+        <v>-1.7288123177163911E-2</v>
+      </c>
+      <c r="Y10" s="2">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="Z10">
+        <v>9</v>
+      </c>
+      <c r="AA10">
+        <v>19</v>
+      </c>
+      <c r="AB10">
+        <v>2</v>
+      </c>
+      <c r="AC10" s="2">
+        <v>0.79850374064837903</v>
+      </c>
+      <c r="AD10" s="2">
+        <v>0.7760652765185857</v>
+      </c>
+      <c r="AE10" s="2">
+        <v>0.80431266846361182</v>
+      </c>
+      <c r="AF10" s="2">
+        <v>0.80260617760617758</v>
+      </c>
+      <c r="AG10" s="2">
+        <v>0.82376150811047788</v>
+      </c>
+      <c r="AH10" s="2">
+        <v>0.95128044971892567</v>
+      </c>
+      <c r="AI10" s="2">
+        <v>0.45034353529044352</v>
+      </c>
+      <c r="AJ10" s="2">
+        <v>0.2857142857142857</v>
+      </c>
+      <c r="AK10" s="2">
+        <v>0.7</v>
+      </c>
+      <c r="AL10" s="2">
+        <v>0.90476190476190477</v>
+      </c>
+    </row>
+    <row r="11" spans="1:38" x14ac:dyDescent="0.35">
+      <c r="A11" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="B10">
+      <c r="B11">
         <v>2005</v>
       </c>
-      <c r="C10">
+      <c r="C11">
         <v>2281</v>
       </c>
-      <c r="D10">
+      <c r="D11">
         <v>1601</v>
       </c>
-      <c r="E10">
+      <c r="E11">
         <v>513</v>
       </c>
-      <c r="F10">
+      <c r="F11">
         <v>603</v>
       </c>
-      <c r="G10">
+      <c r="G11">
         <v>2132</v>
       </c>
-      <c r="H10">
+      <c r="H11">
         <v>444</v>
       </c>
-      <c r="I10" s="2">
+      <c r="I11" s="2">
         <v>1.1376558603491269</v>
       </c>
-      <c r="J10">
+      <c r="J11">
         <v>2206</v>
       </c>
-      <c r="K10">
+      <c r="K11">
         <v>7</v>
       </c>
-      <c r="L10">
+      <c r="L11">
         <v>1899</v>
       </c>
-      <c r="M10" s="2">
+      <c r="M11" s="2">
         <v>0.61748629631573093</v>
       </c>
-      <c r="N10" s="2">
+      <c r="N11" s="2">
         <v>0.35579142550169751</v>
       </c>
-      <c r="O10" s="2">
+      <c r="O11" s="2">
         <v>0.45392700205696002</v>
       </c>
-      <c r="P10">
-        <v>0</v>
-      </c>
-      <c r="Q10" s="2">
-        <v>1</v>
-      </c>
-      <c r="R10" s="2">
-        <v>1</v>
-      </c>
-      <c r="S10" s="2">
-        <v>1</v>
-      </c>
-      <c r="T10" s="2">
-        <v>1</v>
-      </c>
-      <c r="U10">
+      <c r="P11">
+        <v>0</v>
+      </c>
+      <c r="Q11" s="2">
+        <v>1</v>
+      </c>
+      <c r="R11" s="2">
+        <v>1</v>
+      </c>
+      <c r="S11" s="2">
+        <v>1</v>
+      </c>
+      <c r="T11" s="2">
+        <v>1</v>
+      </c>
+      <c r="U11">
         <v>1855</v>
       </c>
-      <c r="V10">
+      <c r="V11">
         <v>2072</v>
       </c>
-      <c r="W10" s="2">
-        <v>1</v>
-      </c>
-      <c r="X10" s="2">
-        <v>1</v>
-      </c>
-      <c r="Y10" s="2">
-        <v>1</v>
-      </c>
-      <c r="Z10">
-        <v>0</v>
-      </c>
-      <c r="AA10">
+      <c r="W11" s="2">
+        <v>1</v>
+      </c>
+      <c r="X11" s="2">
+        <v>1</v>
+      </c>
+      <c r="Y11" s="2">
+        <v>1</v>
+      </c>
+      <c r="Z11">
+        <v>0</v>
+      </c>
+      <c r="AA11">
         <v>30</v>
       </c>
-      <c r="AB10">
-        <v>0</v>
-      </c>
-      <c r="AC10" s="2">
-        <v>1</v>
-      </c>
-      <c r="AD10" s="2">
-        <v>1</v>
-      </c>
-      <c r="AE10" s="2">
-        <v>1</v>
-      </c>
-      <c r="AF10" s="2">
-        <v>1</v>
-      </c>
-      <c r="AG10" s="2">
-        <v>1</v>
-      </c>
-      <c r="AH10" s="2">
+      <c r="AB11">
+        <v>0</v>
+      </c>
+      <c r="AC11" s="2">
+        <v>1</v>
+      </c>
+      <c r="AD11" s="2">
+        <v>1</v>
+      </c>
+      <c r="AE11" s="2">
+        <v>1</v>
+      </c>
+      <c r="AF11" s="2">
+        <v>1</v>
+      </c>
+      <c r="AG11" s="2">
+        <v>1</v>
+      </c>
+      <c r="AH11" s="2">
         <v>0.79850374064837903</v>
       </c>
-      <c r="AI10" s="2">
+      <c r="AI11" s="2">
         <v>0.30074812967581049</v>
       </c>
-      <c r="AJ10" s="2">
-        <v>1</v>
-      </c>
-      <c r="AK10" s="2">
-        <v>1</v>
-      </c>
-      <c r="AL10" s="2">
+      <c r="AJ11" s="2">
+        <v>1</v>
+      </c>
+      <c r="AK11" s="2">
+        <v>1</v>
+      </c>
+      <c r="AL11" s="2">
         <v>1</v>
       </c>
     </row>
